--- a/tame_output/ON/bt/strategyON_20230731.xlsx
+++ b/tame_output/ON/bt/strategyON_20230731.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,16 +758,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.8%</t>
+          <t>456.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>105.2%</t>
+          <t>104.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>141.8%</t>
+          <t>141.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>136.2%</t>
+          <t>135.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1674"/>
+  <dimension ref="A1:G1675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40012,7 +40012,7 @@
         <v>45136</v>
       </c>
       <c r="B1674" t="n">
-        <v>2.881825636771628</v>
+        <v>2.881716008181036</v>
       </c>
       <c r="C1674" t="n">
         <v>3.01726279950454</v>
@@ -40028,6 +40028,29 @@
       </c>
       <c r="G1674" t="n">
         <v>4.295221009612608</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="2" t="n">
+        <v>45137</v>
+      </c>
+      <c r="B1675" t="n">
+        <v>2.885843256651356</v>
+      </c>
+      <c r="C1675" t="n">
+        <v>3.005015340003198</v>
+      </c>
+      <c r="D1675" t="n">
+        <v>1.515451384601761</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>3.610839469530156</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>2.12993035018011</v>
+      </c>
+      <c r="G1675" t="n">
+        <v>4.282973550111265</v>
       </c>
     </row>
   </sheetData>
